--- a/toms_category_mapping_template.xlsx
+++ b/toms_category_mapping_template.xlsx
@@ -427,13 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,6 +458,11 @@
           <t>ID Shopee Category id</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sizechart Images</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -476,6 +482,11 @@
       </c>
       <c r="D2" t="n">
         <v>100591</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://example.com/sizechart.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -489,13 +500,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,6 +531,11 @@
           <t>ID Lazada Category id</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sizechart Images</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -538,6 +555,11 @@
       </c>
       <c r="D2" t="n">
         <v>14883</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://example.com/sizechart.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -551,13 +573,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,6 +604,11 @@
           <t>ID Tiktok Category id</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sizechart Images</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,6 +629,11 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>Sepatu Wanita/Sepatu Mary Jane</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://example.com/sizechart.jpg</t>
         </is>
       </c>
     </row>
@@ -615,13 +648,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,6 +679,11 @@
           <t>ID Zalora Category id</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sizechart Images</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -665,6 +704,11 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>2171 - Sepatu / Sepatu Wanita / Slip On</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://example.com/sizechart.jpg</t>
         </is>
       </c>
     </row>
